--- a/artfynd/A 22876-2024 artfynd.xlsx
+++ b/artfynd/A 22876-2024 artfynd.xlsx
@@ -915,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118264788</v>
+        <v>118264816</v>
       </c>
       <c r="B4" t="n">
-        <v>100017</v>
+        <v>103349</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,16 +931,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222771</v>
+        <v>222412</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -952,7 +952,7 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
@@ -1035,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118264816</v>
+        <v>118264788</v>
       </c>
       <c r="B5" t="n">
-        <v>103349</v>
+        <v>100017</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,16 +1051,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222412</v>
+        <v>222771</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1072,7 +1072,7 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>

--- a/artfynd/A 22876-2024 artfynd.xlsx
+++ b/artfynd/A 22876-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118264786</v>
+        <v>118264877</v>
       </c>
       <c r="B2" t="n">
-        <v>104853</v>
+        <v>108453</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221141</v>
+        <v>220204</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,8 +708,16 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -719,14 +727,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Rönnestad, 240 m NV, Ög</t>
+          <t>Svärdstorp, 460 m SO, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>491857</v>
+        <v>491644</v>
       </c>
       <c r="R2" t="n">
-        <v>6442318</v>
+        <v>6442596</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -773,7 +781,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Lundmiljö</t>
+          <t>Igenväxande skogsbete</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -795,10 +803,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118264790</v>
+        <v>118264816</v>
       </c>
       <c r="B3" t="n">
-        <v>100107</v>
+        <v>103349</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,28 +819,28 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
@@ -915,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118264816</v>
+        <v>118264788</v>
       </c>
       <c r="B4" t="n">
-        <v>103349</v>
+        <v>100017</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,16 +939,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222412</v>
+        <v>222771</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -952,7 +960,7 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
@@ -1035,10 +1043,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118264788</v>
+        <v>118264786</v>
       </c>
       <c r="B5" t="n">
-        <v>100017</v>
+        <v>104853</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,16 +1059,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222771</v>
+        <v>221141</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1072,7 +1080,7 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
@@ -1275,10 +1283,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118264877</v>
+        <v>118264790</v>
       </c>
       <c r="B7" t="n">
-        <v>108453</v>
+        <v>100107</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1287,37 +1295,29 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220204</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -1327,14 +1327,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Svärdstorp, 460 m SO, Ög</t>
+          <t>Rönnestad, 240 m NV, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>491644</v>
+        <v>491857</v>
       </c>
       <c r="R7" t="n">
-        <v>6442596</v>
+        <v>6442318</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Igenväxande skogsbete</t>
+          <t>Lundmiljö</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
